--- a/samples/고충민원_2_민원처리대장_2026년3분기.xlsx
+++ b/samples/고충민원_2_민원처리대장_2026년3분기.xlsx
@@ -2556,7 +2556,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>02-000-0009</t>
+          <t>01000000009</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
